--- a/V. 2 (Pudim)/dados_teste/DADOS_V2_PUDIM_bp-dre4.xlsx
+++ b/V. 2 (Pudim)/dados_teste/DADOS_V2_PUDIM_bp-dre4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ferna\Documents\dev\Finscore\FinScore\V. 2 (Pudim)\dados_teste\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C97B078A-BBD1-4252-A3BA-0AF0BEC1A1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6176CFCB-FCB8-4681-BC28-6912174C95DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="103">
   <si>
     <t>ano</t>
   </si>
@@ -1000,12 +1000,15 @@
   <si>
     <t>r_Despesa_de_Impostos</t>
   </si>
+  <si>
+    <t>r_Despesa_IR_CSLL</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1024,20 +1027,20 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
@@ -1050,13 +1053,13 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1085,13 +1088,6 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1143,7 +1139,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1198,9 +1194,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1552,8 +1545,8 @@
       <c r="T1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="20" t="s">
-        <v>101</v>
+      <c r="U1" s="9" t="s">
+        <v>102</v>
       </c>
       <c r="V1" s="9" t="s">
         <v>17</v>
